--- a/sheets/민요/검수/새 타령.xlsx
+++ b/sheets/민요/검수/새 타령.xlsx
@@ -4,17 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
-    <sheet name="악보 3" sheetId="5" r:id="rId5"/>
-    <sheet name="악보 4" sheetId="6" r:id="rId6"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -23,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -53,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -76,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +176,72 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7376,8 +7519,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U56"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -7400,2383 +7547,2410 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새 타령 — 민요채보-2/새 타령.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">새 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쌍</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 南</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">문</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="R3" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="S3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">온</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="T3" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="U3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="18"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="G4" s="24"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="S4" s="23"/>
+      <c r="T4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="U4" s="23"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="18"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="Q5" s="25"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="25"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 潢</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 潢</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쌍</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="L6" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">곡</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">문</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="P6" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">잡</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="T6" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="U6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="18"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="U7" s="23"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="18"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="25"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="C9" s="21"/>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="I9" s="21"/>
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">뭇</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 黃</t>
         </is>
       </c>
-      <c r="S9" s="2"/>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="S9" s="21"/>
+      <c r="T9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="U9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="18"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G10" s="23"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="S10" s="23"/>
+      <c r="T10" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U10" s="23"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃
 無</t>
         </is>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="G11" s="25"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U11" s="25"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">득</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">초</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃
 無</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="O12" s="21"/>
+      <c r="P12" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="Q12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="R12" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="S12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="T12" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="U12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E13" s="23"/>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G13" s="23"/>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="23"/>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K13" s="23"/>
+      <c r="L13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="M13" s="23"/>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O13" s="23"/>
+      <c r="P13" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S13" s="23"/>
+      <c r="T13" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U13" s="23"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="25"/>
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="25"/>
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="25"/>
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="25"/>
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="25"/>
+      <c r="L14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="M14" s="25"/>
+      <c r="N14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="O14" s="25"/>
+      <c r="P14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="Q14" s="25"/>
+      <c r="R14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="S14" s="25"/>
+      <c r="T14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새 타령 — 민요채보-2/새 타령.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="U14" s="25"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">새 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C16"/>
+      <c s="8" r="D16"/>
+      <c s="8" r="E16"/>
+      <c s="8" r="F16"/>
+      <c s="8" r="G16"/>
+      <c s="8" r="H16"/>
+      <c s="8" r="I16"/>
+      <c s="8" r="J16"/>
+      <c s="8" r="K16"/>
+      <c s="8" r="L16"/>
+      <c s="8" r="M16"/>
+      <c s="8" r="N16"/>
+      <c s="8" r="O16"/>
+      <c s="8" r="P16"/>
+      <c s="8" r="Q16"/>
+      <c s="8" r="R16"/>
+      <c s="8" r="S16"/>
+      <c s="8" r="T16"/>
+      <c s="8" r="U16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="20"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 潢</t>
         </is>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="Q17" s="21"/>
+      <c r="R17" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 潢</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="S17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="T17" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="U17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">쳐</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="20"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="18"/>
+      <c r="U18" s="23"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="20"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="25"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="20"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="Q20" s="21"/>
+      <c r="R20" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 潢</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="S20" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="T20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="U20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="20"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="23"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="23"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="20"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="25"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="B23" s="20"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃
 無</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="Q23" s="22"/>
+      <c r="R23" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃
 無</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="S23" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="T23" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="U23" s="21"/>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="B24" s="20"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="23"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="B25" s="20"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="25"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="B26" s="20"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="S26" s="21"/>
+      <c r="T26" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="U26" s="21"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="B27" s="20"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="S27" s="23"/>
+      <c r="T27" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="U27" s="23"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="B28" s="20"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="Q28" s="25"/>
+      <c r="R28" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="S28" s="25"/>
+      <c r="T28" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
-    <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
-    <col min="21" max="21" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새 타령 — 민요채보-2/새 타령-2.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="U28" s="25"/>
+    </row>
+    <row r="29"/>
+    <row r="30" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B30">
+        <is>
+          <t xml:space="preserve">새 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C30"/>
+      <c s="8" r="D30"/>
+      <c s="8" r="E30"/>
+      <c s="8" r="F30"/>
+      <c s="8" r="G30"/>
+      <c s="8" r="H30"/>
+      <c s="8" r="I30"/>
+      <c s="8" r="J30"/>
+      <c s="8" r="K30"/>
+      <c s="8" r="L30"/>
+      <c s="8" r="M30"/>
+      <c s="8" r="N30"/>
+      <c s="8" r="O30"/>
+      <c s="8" r="P30"/>
+      <c s="8" r="Q30"/>
+      <c s="8" r="R30"/>
+      <c s="8" r="S30"/>
+      <c s="8" r="T30"/>
+      <c s="8" r="U30"/>
+    </row>
+    <row r="31" ht="56" customHeight="1">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 潢</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좌</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 潢</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="K31" s="22"/>
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="M31" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="N31" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="O31" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="P31" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="Q31" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="R31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S31" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="U31" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">붕</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+    <row r="32" ht="56" customHeight="1">
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="E32" s="23"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="K32" s="23"/>
+      <c r="L32" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="M32" s="23"/>
+      <c r="N32" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 南</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="O32" s="23"/>
+      <c r="P32" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="Q32" s="23"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="23"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="23"/>
+    </row>
+    <row r="33" ht="56" customHeight="1">
+      <c r="B33" s="18"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="E33" s="25"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="25"/>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃
 南</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D34" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 無</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F34" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G34" s="21"/>
+      <c r="H34" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="I34" s="21"/>
+      <c r="J34" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="K34" s="21"/>
+      <c r="L34" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 無</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M34" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">뻐</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3" t="inlineStr">
+      <c r="N34" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="O34" s="22"/>
+      <c r="P34" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="S34" s="22"/>
+      <c r="T34" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="U34" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+    <row r="35" ht="56" customHeight="1">
+      <c r="B35" s="18"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="E35" s="23"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K35" s="23"/>
+      <c r="L35" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 無</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M35" s="23"/>
+      <c r="N35" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 㳞</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="O35" s="23"/>
+      <c r="P35" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="23"/>
+    </row>
+    <row r="36" ht="56" customHeight="1">
+      <c r="B36" s="18"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="25"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="18"/>
+      <c r="S36" s="25"/>
+      <c r="T36" s="18"/>
+      <c r="U36" s="25"/>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 黃</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E37" s="21"/>
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="G37" s="21"/>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="I37" s="21"/>
+      <c r="J37" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="K37" s="21"/>
+      <c r="L37" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="M37" s="21"/>
+      <c r="N37" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="O37" s="21"/>
+      <c r="P37" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q37" s="21"/>
+      <c r="R37" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="S9" s="2"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S37" s="21"/>
+      <c r="T37" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="U37" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="38" ht="56" customHeight="1">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C38" s="23"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="23"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="23"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="23"/>
+    </row>
+    <row r="39" ht="56" customHeight="1">
+      <c r="B39" s="18"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="25"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="25"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="25"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="25"/>
+    </row>
+    <row r="40" ht="56" customHeight="1">
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C40" s="21"/>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E40" s="21"/>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G40" s="21"/>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I40" s="21"/>
+      <c r="J40" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K40" s="21"/>
+      <c r="L40" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M40" s="21"/>
+      <c r="N40" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O40" s="21"/>
+      <c r="P40" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q40" s="21"/>
+      <c r="R40" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S40" s="21"/>
+      <c r="T40" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U40" s="21"/>
+    </row>
+    <row r="41" ht="56" customHeight="1">
+      <c r="B41" s="18"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="23"/>
+      <c r="R41" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S41" s="23"/>
+      <c r="T41" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U41" s="23"/>
+    </row>
+    <row r="42" ht="56" customHeight="1">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C42" s="25"/>
+      <c r="D42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E42" s="25"/>
+      <c r="F42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G42" s="25"/>
+      <c r="H42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I42" s="25"/>
+      <c r="J42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K42" s="25"/>
+      <c r="L42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="M42" s="25"/>
+      <c r="N42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="O42" s="25"/>
+      <c r="P42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="Q42" s="25"/>
+      <c r="R42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="S42" s="25"/>
+      <c r="T42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새 타령 — 민요채보-2/새 타령-2.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="U42" s="25"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B44">
+        <is>
+          <t xml:space="preserve">새 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C44"/>
+      <c s="8" r="D44"/>
+      <c s="8" r="E44"/>
+      <c s="8" r="F44"/>
+      <c s="8" r="G44"/>
+      <c s="8" r="H44"/>
+      <c s="8" r="I44"/>
+      <c s="8" r="J44"/>
+      <c s="8" r="K44"/>
+      <c s="8" r="L44"/>
+      <c s="8" r="M44"/>
+      <c s="8" r="N44"/>
+      <c s="8" r="O44"/>
+      <c s="8" r="P44"/>
+      <c s="8" r="Q44"/>
+      <c s="8" r="R44"/>
+      <c s="8" r="S44"/>
+      <c s="8" r="T44"/>
+      <c s="8" r="U44"/>
+    </row>
+    <row r="45" ht="56" customHeight="1">
+      <c r="B45" s="20"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="O45" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="P45" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 潢</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="Q45" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="R45" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="S45" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="T45" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="U45" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+    <row r="46" ht="56" customHeight="1">
+      <c r="B46" s="20"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="27"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="27"/>
+      <c r="N46" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="O46" s="23"/>
+      <c r="P46" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">浹</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="Q46" s="23"/>
+      <c r="R46" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="S46" s="23"/>
+      <c r="T46" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="U46" s="23"/>
+    </row>
+    <row r="47" ht="56" customHeight="1">
+      <c r="B47" s="20"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="28"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="25"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="25"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="25"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="25"/>
+    </row>
+    <row r="48" ht="56" customHeight="1">
+      <c r="B48" s="20"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="26"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 黃
 無</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="O48" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="P48" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 黃</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="Q48" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="R48" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 潢</t>
         </is>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="S48" s="22"/>
+      <c r="T48" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 㳞</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="U48" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="49" ht="56" customHeight="1">
+      <c r="B49" s="20"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="27"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="O49" s="23"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="23"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="23"/>
+      <c r="T49" s="18"/>
+      <c r="U49" s="23"/>
+    </row>
+    <row r="50" ht="56" customHeight="1">
+      <c r="B50" s="20"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="18"/>
+      <c r="O50" s="25"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="25"/>
+      <c r="R50" s="18"/>
+      <c r="S50" s="25"/>
+      <c r="T50" s="18"/>
+      <c r="U50" s="25"/>
+    </row>
+    <row r="51" ht="56" customHeight="1">
+      <c r="B51" s="20"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="26"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="O51" s="21"/>
+      <c r="P51" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 黃</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="Q51" s="21"/>
+      <c r="R51" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="S51" s="21"/>
+      <c r="T51" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="U51" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="52" ht="56" customHeight="1">
+      <c r="B52" s="20"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="27"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="27"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="27"/>
+      <c r="N52" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">夾</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="O52" s="23"/>
+      <c r="P52" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="Q52" s="23"/>
+      <c r="R52" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="S52" s="23"/>
+      <c r="T52" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夾</t>
+        </is>
+      </c>
+      <c r="U52" s="23"/>
+    </row>
+    <row r="53" ht="56" customHeight="1">
+      <c r="B53" s="20"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="28"/>
+      <c r="L53" s="20"/>
+      <c r="M53" s="28"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="25"/>
+      <c r="P53" s="18"/>
+      <c r="Q53" s="25"/>
+      <c r="R53" s="18"/>
+      <c r="S53" s="25"/>
+      <c r="T53" s="18"/>
+      <c r="U53" s="25"/>
+    </row>
+    <row r="54" ht="56" customHeight="1">
+      <c r="B54" s="20"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O54" s="21"/>
+      <c r="P54" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q54" s="21"/>
+      <c r="R54" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S54" s="21"/>
+      <c r="T54" s="18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U54" s="21"/>
+    </row>
+    <row r="55" ht="56" customHeight="1">
+      <c r="B55" s="20"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="27"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="27"/>
+      <c r="L55" s="20"/>
+      <c r="M55" s="27"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="23"/>
+      <c r="P55" s="18"/>
+      <c r="Q55" s="23"/>
+      <c r="R55" s="18"/>
+      <c r="S55" s="23"/>
+      <c r="T55" s="18"/>
+      <c r="U55" s="23"/>
+    </row>
+    <row r="56" ht="56" customHeight="1">
+      <c r="B56" s="20"/>
+      <c r="C56" s="28"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="28"/>
+      <c r="N56" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="O56" s="25"/>
+      <c r="P56" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="Q56" s="25"/>
+      <c r="R56" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="S56" s="25"/>
+      <c r="T56" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
+      <c r="U56" s="25"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B16:U16"/>
+    <mergeCell ref="B30:U30"/>
+    <mergeCell ref="B44:U44"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="14" max="16383" man="1"/>
+    <brk id="28" max="16383" man="1"/>
+    <brk id="42" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/새 타령.xlsx
+++ b/sheets/민요/검수/새 타령.xlsx
@@ -417,7 +417,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="2"/>
@@ -744,12 +744,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -858,12 +858,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="2"/>
@@ -893,12 +893,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="2"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="2"/>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I18" s="2"/>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I26" s="2"/>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I32" s="2"/>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I46" s="2"/>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I66" s="2"/>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I69" s="2"/>
@@ -3330,12 +3330,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I72" s="2"/>
@@ -3447,12 +3447,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I75" s="2"/>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I82" s="2"/>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I97" s="2"/>
@@ -4548,7 +4548,7 @@
       <c r="E4" s="9"/>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G4" s="9"/>
@@ -4602,7 +4602,7 @@
       <c r="Q4" s="12"/>
       <c r="R4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S4" s="9"/>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="10"/>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="10"/>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q5" s="10"/>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="T5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U5" s="10"/>
@@ -4830,7 +4830,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr">
@@ -4885,7 +4885,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="10"/>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="10"/>
@@ -4951,13 +4951,13 @@
       </c>
       <c r="R8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S8" s="10"/>
       <c r="T8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U8" s="10"/>
@@ -5160,13 +5160,13 @@
       <c r="E11" s="10"/>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="10"/>
@@ -5194,7 +5194,7 @@
       <c r="O11" s="10"/>
       <c r="P11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q11" s="10"/>
@@ -5206,7 +5206,7 @@
       <c r="S11" s="10"/>
       <c r="T11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U11" s="10"/>
@@ -5235,13 +5235,13 @@
       <c r="Q12" s="8"/>
       <c r="R12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S12" s="8"/>
       <c r="T12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U12" s="8"/>

--- a/sheets/민요/검수/새 타령.xlsx
+++ b/sheets/민요/검수/새 타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,39 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4409,124 +4456,124 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">새 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우을</t>
         </is>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="D3" s="23"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">쌍</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우을</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="P3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="R3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="R3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="S3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">온</t>
         </is>
       </c>
-      <c r="T3" s="18" t="inlineStr">
+      <c r="T3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U3" s="11" t="inlineStr">
+      <c r="U3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4534,261 +4581,261 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="D4" s="23"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="G4" s="26"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리임</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">흔</t>
         </is>
       </c>
-      <c r="L4" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="N4" s="18" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="P4" s="18" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="Q4" s="25"/>
+      <c r="R4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="S4" s="26"/>
+      <c r="T4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U4" s="9"/>
+      <c r="U4" s="26"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="C5" s="27"/>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">거어</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="I5" s="27"/>
+      <c r="J5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="K5" s="16" t="inlineStr">
+      <c r="K5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="27"/>
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">문</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="18" t="inlineStr">
+      <c r="Q5" s="27"/>
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 無</t>
         </is>
       </c>
-      <c r="S5" s="13" t="inlineStr">
+      <c r="S5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">갓</t>
         </is>
       </c>
-      <c r="T5" s="17" t="inlineStr">
+      <c r="T5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U5" s="10"/>
+      <c r="U5" s="27"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="C6" s="24"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쌍</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">답</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="18" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M6" s="24"/>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="P6" s="18" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="R6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="S6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">잡</t>
         </is>
       </c>
-      <c r="T6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4796,265 +4843,265 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="C7" s="26"/>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="26"/>
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="18" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O7" s="26"/>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q7" s="12" t="inlineStr">
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="R7" s="18" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S7" s="12" t="inlineStr">
+      <c r="S7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="T7" s="17" t="inlineStr">
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U7" s="9"/>
+      <c r="U7" s="26"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="C8" s="27"/>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="I8" s="27"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="K8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">쪼오</t>
         </is>
       </c>
-      <c r="L8" s="17"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="18" t="inlineStr">
+      <c r="L8" s="23"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">꾸</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="R8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S8" s="10"/>
-      <c r="T8" s="17" t="inlineStr">
+      <c r="S8" s="27"/>
+      <c r="T8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U8" s="10"/>
+      <c r="U8" s="27"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="B9" s="23"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">을우ㅁ</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">날아</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="I9" s="22"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">뭇</t>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">무두</t>
         </is>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">웅</t>
         </is>
       </c>
-      <c r="P9" s="18" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="11" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
       </c>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="R9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="S9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">날아</t>
         </is>
       </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="T9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="U9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">날아</t>
         </is>
@@ -5062,87 +5109,87 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="B10" s="23"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">윤</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G10" s="26"/>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이인</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="N10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">변</t>
         </is>
       </c>
-      <c r="P10" s="18" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q10" s="12" t="inlineStr">
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">황</t>
         </is>
       </c>
-      <c r="R10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="S10" s="9" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="S10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
       </c>
-      <c r="T10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U10" s="9" t="inlineStr">
+      <c r="T10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
@@ -5150,225 +5197,225 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="B11" s="23"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="27"/>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="27"/>
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="I11" s="27"/>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="M11" s="27"/>
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="O11" s="27"/>
+      <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="Q11" s="27"/>
+      <c r="R11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S11" s="10"/>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="S11" s="27"/>
+      <c r="T11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U11" s="10"/>
+      <c r="U11" s="27"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="B12" s="23"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="K12" s="24"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S12" s="8"/>
-      <c r="T12" s="17" t="inlineStr">
+      <c r="S12" s="24"/>
+      <c r="T12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U12" s="8"/>
+      <c r="U12" s="24"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="9"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="26"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">어어</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">초</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="K14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L14" s="18" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M14" s="13" t="inlineStr">
+      <c r="M14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">초</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="P14" s="18" t="inlineStr">
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="Q14" s="13" t="inlineStr">
+      <c r="Q14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="R14" s="18" t="inlineStr">
+      <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S14" s="13" t="inlineStr">
+      <c r="S14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="T14" s="18" t="inlineStr">
+      <c r="T14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U14" s="13" t="inlineStr">
+      <c r="U14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>

--- a/sheets/민요/검수/새 타령.xlsx
+++ b/sheets/민요/검수/새 타령.xlsx
@@ -4429,32 +4429,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4655,16 +4655,16 @@
       <c r="S4" s="26"/>
       <c r="T4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U4" s="26"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="27"/>
@@ -4713,7 +4713,7 @@
       <c r="M5" s="27"/>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O5" s="27" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="U5" s="27"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C6" s="24"/>
@@ -4841,11 +4841,11 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C7" s="26"/>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="T7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U7" s="26"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="P8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q8" s="27" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="U8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23"/>
       <c r="C9" s="24"/>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23"/>
       <c r="C10" s="26"/>
@@ -5195,13 +5195,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23"/>
       <c r="C11" s="27"/>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E11" s="27"/>
@@ -5229,13 +5229,13 @@
       </c>
       <c r="L11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M11" s="27"/>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O11" s="27"/>
@@ -5247,7 +5247,7 @@
       <c r="Q11" s="27"/>
       <c r="R11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S11" s="27"/>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="U11" s="27"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23"/>
       <c r="C12" s="24"/>
@@ -5270,7 +5270,7 @@
       <c r="I12" s="24"/>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K12" s="24"/>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="U12" s="24"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
       <c r="C13" s="26"/>
@@ -5316,7 +5316,7 @@
       <c r="T13" s="23"/>
       <c r="U13" s="26"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/새 타령.xlsx
+++ b/sheets/민요/검수/새 타령.xlsx
@@ -4491,7 +4491,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우을</t>
+          <t xml:space="preserve">우
+을</t>
         </is>
       </c>
       <c r="D3" s="23"/>
@@ -4514,7 +4515,8 @@
       </c>
       <c r="I3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우을</t>
+          <t xml:space="preserve">우
+을</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
@@ -4607,7 +4609,8 @@
       </c>
       <c r="I4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">리임</t>
+          <t xml:space="preserve">리
+임</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
@@ -4686,7 +4689,8 @@
       </c>
       <c r="G5" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">거어</t>
+          <t xml:space="preserve">거
+어</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
@@ -4970,7 +4974,8 @@
       </c>
       <c r="K8" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">쪼오</t>
+          <t xml:space="preserve">쪼
+오</t>
         </is>
       </c>
       <c r="L8" s="23"/>
@@ -5021,7 +5026,9 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">을우ㅁ</t>
+          <t xml:space="preserve">을
+우
+ㅁ</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -5032,7 +5039,8 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">날아</t>
+          <t xml:space="preserve">날
+아</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -5060,7 +5068,8 @@
       </c>
       <c r="M9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">무두</t>
+          <t xml:space="preserve">무
+두</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -5092,7 +5101,8 @@
       </c>
       <c r="S9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">날아</t>
+          <t xml:space="preserve">날
+아</t>
         </is>
       </c>
       <c r="T9" s="23" t="inlineStr">
@@ -5103,7 +5113,8 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">날아</t>
+          <t xml:space="preserve">날
+아</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5162,8 @@
       </c>
       <c r="M10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">이인</t>
+          <t xml:space="preserve">이
+인</t>
         </is>
       </c>
       <c r="N10" s="23" t="inlineStr">
@@ -5326,7 +5338,8 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">어어</t>
+          <t xml:space="preserve">어
+어</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">

--- a/sheets/민요/검수/새 타령.xlsx
+++ b/sheets/민요/검수/새 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,6 +247,27 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4489,20 +4515,20 @@
 潢</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 을</t>
         </is>
       </c>
       <c r="D3" s="23"/>
-      <c r="E3" s="24"/>
+      <c r="E3" s="32"/>
       <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">쌍</t>
         </is>
@@ -4513,7 +4539,7 @@
 黃</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 을</t>
@@ -4525,7 +4551,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">농</t>
         </is>
@@ -4535,7 +4561,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
@@ -4545,7 +4571,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -4555,7 +4581,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4565,7 +4591,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S3" s="24" t="inlineStr">
+      <c r="S3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">온</t>
         </is>
@@ -4575,7 +4601,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U3" s="22" t="inlineStr">
+      <c r="U3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4588,26 +4614,26 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="D4" s="23"/>
-      <c r="E4" s="26"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="34"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">리
 임</t>
@@ -4619,7 +4645,7 @@
 黃</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">흔</t>
         </is>
@@ -4629,7 +4655,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4639,7 +4665,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -4649,19 +4675,19 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q4" s="25"/>
+      <c r="Q4" s="33"/>
       <c r="R4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S4" s="26"/>
+      <c r="S4" s="34"/>
       <c r="T4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U4" s="26"/>
+      <c r="U4" s="34"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -4670,13 +4696,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -4687,7 +4713,7 @@
 黃</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">거
 어</t>
@@ -4698,13 +4724,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="27"/>
+      <c r="I5" s="35"/>
       <c r="J5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="K5" s="30" t="inlineStr">
+      <c r="K5" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4714,13 +4740,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="27"/>
+      <c r="M5" s="35"/>
       <c r="N5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">문</t>
         </is>
@@ -4730,14 +4756,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="27"/>
+      <c r="Q5" s="35"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 無</t>
         </is>
       </c>
-      <c r="S5" s="28" t="inlineStr">
+      <c r="S5" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">갓</t>
         </is>
@@ -4747,7 +4773,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U5" s="27"/>
+      <c r="U5" s="35"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -4756,13 +4782,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="24"/>
+      <c r="C6" s="32"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
@@ -4772,7 +4798,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">쌍</t>
         </is>
@@ -4783,7 +4809,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -4793,7 +4819,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">답</t>
         </is>
@@ -4803,13 +4829,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M6" s="24"/>
+      <c r="M6" s="32"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -4819,7 +4845,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4829,7 +4855,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S6" s="24" t="inlineStr">
+      <c r="S6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">잡</t>
         </is>
@@ -4839,7 +4865,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U6" s="24" t="inlineStr">
+      <c r="U6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4852,13 +4878,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C7" s="26"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4868,7 +4894,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
@@ -4878,13 +4904,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I7" s="26"/>
+      <c r="I7" s="34"/>
       <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="K7" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4894,7 +4920,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M7" s="26" t="inlineStr">
+      <c r="M7" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
@@ -4904,13 +4930,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O7" s="26"/>
+      <c r="O7" s="34"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="Q7" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4920,7 +4946,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S7" s="25" t="inlineStr">
+      <c r="S7" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4930,7 +4956,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U7" s="26"/>
+      <c r="U7" s="34"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -4939,13 +4965,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4955,7 +4981,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -4965,28 +4991,28 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="27"/>
+      <c r="I8" s="35"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K8" s="28" t="inlineStr">
+      <c r="K8" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">쪼
 오</t>
         </is>
       </c>
       <c r="L8" s="23"/>
-      <c r="M8" s="27"/>
+      <c r="M8" s="35"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O8" s="28" t="inlineStr">
+      <c r="O8" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">꾸</t>
         </is>
@@ -4996,7 +5022,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q8" s="27" t="inlineStr">
+      <c r="Q8" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -5006,25 +5032,25 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S8" s="27"/>
+      <c r="S8" s="35"/>
       <c r="T8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U8" s="27"/>
+      <c r="U8" s="35"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
+      <c r="C9" s="32"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">을
 우
@@ -5037,7 +5063,7 @@
 無</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">날
 아</t>
@@ -5049,13 +5075,13 @@
 無</t>
         </is>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="31"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">뭇</t>
         </is>
@@ -5066,7 +5092,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">무
 두</t>
@@ -5078,7 +5104,7 @@
 無</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">웅</t>
         </is>
@@ -5088,7 +5114,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
@@ -5099,7 +5125,7 @@
 南</t>
         </is>
       </c>
-      <c r="S9" s="24" t="inlineStr">
+      <c r="S9" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">날
 아</t>
@@ -5111,7 +5137,7 @@
 南</t>
         </is>
       </c>
-      <c r="U9" s="24" t="inlineStr">
+      <c r="U9" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">날
 아</t>
@@ -5121,13 +5147,13 @@
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23"/>
-      <c r="C10" s="26"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">윤</t>
         </is>
@@ -5137,19 +5163,19 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I10" s="26"/>
+      <c r="I10" s="34"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -5160,7 +5186,7 @@
 無</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 인</t>
@@ -5171,7 +5197,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O10" s="26" t="inlineStr">
+      <c r="O10" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">변</t>
         </is>
@@ -5181,7 +5207,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="Q10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">황</t>
         </is>
@@ -5191,7 +5217,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S10" s="26" t="inlineStr">
+      <c r="S10" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
@@ -5201,7 +5227,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U10" s="26" t="inlineStr">
+      <c r="U10" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
@@ -5210,31 +5236,31 @@
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23"/>
-      <c r="C11" s="27"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E11" s="27"/>
+      <c r="E11" s="35"/>
       <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="27"/>
+      <c r="I11" s="35"/>
       <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="K11" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
@@ -5244,89 +5270,89 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M11" s="27"/>
+      <c r="M11" s="35"/>
       <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O11" s="27"/>
+      <c r="O11" s="35"/>
       <c r="P11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q11" s="27"/>
+      <c r="Q11" s="35"/>
       <c r="R11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S11" s="27"/>
+      <c r="S11" s="35"/>
       <c r="T11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U11" s="27"/>
+      <c r="U11" s="35"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
+      <c r="C12" s="32"/>
       <c r="D12" s="23"/>
-      <c r="E12" s="24"/>
+      <c r="E12" s="32"/>
       <c r="F12" s="23"/>
-      <c r="G12" s="24"/>
+      <c r="G12" s="32"/>
       <c r="H12" s="23"/>
-      <c r="I12" s="24"/>
+      <c r="I12" s="32"/>
       <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K12" s="24"/>
+      <c r="K12" s="32"/>
       <c r="L12" s="23"/>
-      <c r="M12" s="24"/>
+      <c r="M12" s="32"/>
       <c r="N12" s="23"/>
-      <c r="O12" s="24"/>
+      <c r="O12" s="32"/>
       <c r="P12" s="23"/>
-      <c r="Q12" s="24"/>
+      <c r="Q12" s="32"/>
       <c r="R12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S12" s="24"/>
+      <c r="S12" s="32"/>
       <c r="T12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U12" s="24"/>
+      <c r="U12" s="32"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
-      <c r="C13" s="26"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="23"/>
-      <c r="E13" s="26"/>
+      <c r="E13" s="34"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="26"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="23"/>
-      <c r="I13" s="26"/>
+      <c r="I13" s="34"/>
       <c r="J13" s="23"/>
-      <c r="K13" s="26"/>
+      <c r="K13" s="34"/>
       <c r="L13" s="23"/>
-      <c r="M13" s="26"/>
+      <c r="M13" s="34"/>
       <c r="N13" s="23"/>
-      <c r="O13" s="26"/>
+      <c r="O13" s="34"/>
       <c r="P13" s="23"/>
-      <c r="Q13" s="26"/>
+      <c r="Q13" s="34"/>
       <c r="R13" s="23"/>
-      <c r="S13" s="26"/>
+      <c r="S13" s="34"/>
       <c r="T13" s="23"/>
-      <c r="U13" s="26"/>
+      <c r="U13" s="34"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -5336,7 +5362,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 어</t>
@@ -5347,7 +5373,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5357,7 +5383,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
@@ -5367,7 +5393,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">초</t>
         </is>
@@ -5377,7 +5403,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K14" s="28" t="inlineStr">
+      <c r="K14" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5387,7 +5413,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M14" s="28" t="inlineStr">
+      <c r="M14" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">초</t>
         </is>
@@ -5397,7 +5423,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O14" s="27" t="inlineStr">
+      <c r="O14" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -5408,7 +5434,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q14" s="28" t="inlineStr">
+      <c r="Q14" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5418,7 +5444,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S14" s="28" t="inlineStr">
+      <c r="S14" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5428,7 +5454,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U14" s="28" t="inlineStr">
+      <c r="U14" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>

--- a/sheets/민요/검수/새 타령.xlsx
+++ b/sheets/민요/검수/새 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,55 +212,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -366,7 +334,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">97</t>
+          <t xml:space="preserve">115</t>
         </is>
       </c>
     </row>
@@ -378,7 +346,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
@@ -390,7 +358,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -402,7 +370,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">중</t>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
@@ -412,11 +380,7 @@
           <t xml:space="preserve">확인 필요</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">팔레트 외 글자 1, 비고 42%</t>
-        </is>
-      </c>
+      <c r="B12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
@@ -442,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4). 상단 여백에 제목 "새 타령 (굿거리)"와 "C# key ⟷ 6판 c key / 정악 청" 메모. 세로 10줄, 오른쪽부터 1. 각 율명 줄 오른쪽 좁은 칸의 구전 가사를 이미지 그대로 전사함. 중성 南(남려)과 청황 潢이 지배적이고 청성(淋/汰/潢) 변이가 섞임. 요성 물결선·긴 사선 꾸밈·○로 묶은 표시가 여러 칸에 있어 율명에서 빼고 비고에 남김. 흘림체 겹침이 심해 일부 율명·가사는 ?로 둠. AI 재판독.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 한 줄 12정간, 굵은 가로선 3칸마다 → 3/4·12. 오른쪽부터 10줄, 한 곡. 상단에 "새타령(굿거리) 1", "C#key⟷6판 c key / 정악 청" 메모. 율명 옆 작은 ^ 꾸밈은 ^ 로 적음. 潢 아래 無를 쓴 칸(潢|無)의 요성 곡선·10줄 11정간의 ○ 묶음은 생략. 12정간 끝의 D·○ 모양 표시는 쉼 △ 로 적음. 氵 보이는 女古는 㴌, 氵 없는 것은 姑로 구분. 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
@@ -628,26 +592,22 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간 아래 작은 요성 꾸밈</t>
-        </is>
-      </c>
+      <c r="J2" s="4"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -673,12 +633,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I3" s="2"/>
@@ -782,12 +742,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="2"/>
@@ -852,13 +812,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|南</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-南</t>
+無</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -966,15 +926,19 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
@@ -994,31 +958,27 @@
         <v>1</v>
       </c>
       <c r="E12" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 ○</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J12" s="4"/>
       <c r="K12" s="2"/>
     </row>
     <row r="13">
@@ -1031,32 +991,29 @@
         </is>
       </c>
       <c r="C13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">온</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I13" s="2"/>
       <c r="J13" s="4"/>
       <c r="K13" s="2"/>
     </row>
@@ -1076,22 +1033,26 @@
         <v>2</v>
       </c>
       <c r="E14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">온</t>
+        </is>
+      </c>
       <c r="J14" s="4"/>
       <c r="K14" s="2"/>
     </row>
@@ -1111,32 +1072,23 @@
         <v>2</v>
       </c>
       <c r="E15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃|無</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃
-無</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">갓</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃 아래 無, 흐림</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="4"/>
       <c r="K15" s="2"/>
     </row>
     <row r="16">
@@ -1155,24 +1107,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">잡</t>
+          <t xml:space="preserve">갓</t>
         </is>
       </c>
       <c r="J16" s="4"/>
@@ -1194,31 +1147,27 @@
         <v>2</v>
       </c>
       <c r="E17" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 요성 꾸밈</t>
-        </is>
-      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잡</t>
+        </is>
+      </c>
+      <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
     <row r="18">
@@ -1237,22 +1186,26 @@
         <v>2</v>
       </c>
       <c r="E18" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" s="2">
         <v>2</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새</t>
+        </is>
+      </c>
       <c r="J18" s="4"/>
       <c r="K18" s="2"/>
     </row>
@@ -1272,25 +1225,25 @@
         <v>2</v>
       </c>
       <c r="E19" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">날아</t>
+          <t xml:space="preserve">가</t>
         </is>
       </c>
       <c r="J19" s="4"/>
@@ -1312,24 +1265,25 @@
         <v>2</v>
       </c>
       <c r="E20" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" s="2">
         <v>3</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">든</t>
+          <t xml:space="preserve">날아</t>
         </is>
       </c>
       <c r="J20" s="4"/>
@@ -1351,22 +1305,26 @@
         <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" s="2">
         <v>3</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I21" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">든</t>
+        </is>
+      </c>
       <c r="J21" s="4"/>
       <c r="K21" s="2"/>
     </row>
@@ -1386,10 +1344,10 @@
         <v>2</v>
       </c>
       <c r="E22" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1421,31 +1379,27 @@
         <v>2</v>
       </c>
       <c r="E23" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F23" s="2">
         <v>4</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 ○</t>
-        </is>
-      </c>
+      <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
     <row r="24">
@@ -1458,37 +1412,33 @@
         </is>
       </c>
       <c r="C24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간1 상단 요성, 아래 潢</t>
-        </is>
-      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
     <row r="25">
@@ -1501,33 +1451,30 @@
         </is>
       </c>
       <c r="C25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵黃</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="4"/>
       <c r="K25" s="2"/>
     </row>
     <row r="26">
@@ -1546,22 +1493,27 @@
         <v>3</v>
       </c>
       <c r="E26" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">南|–㴌</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I26" s="2"/>
+          <t xml:space="preserve">南
+–㴌</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새에</t>
+        </is>
+      </c>
       <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
@@ -1581,31 +1533,27 @@
         <v>3</v>
       </c>
       <c r="E27" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27" s="2">
-        <v>2</v>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵</t>
-        </is>
-      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="J27" s="4"/>
       <c r="K27" s="2"/>
     </row>
     <row r="28">
@@ -1624,31 +1572,23 @@
         <v>3</v>
       </c>
       <c r="E28" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
     <row r="29">
@@ -1667,19 +1607,19 @@
         <v>3</v>
       </c>
       <c r="E29" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2">
         <v>2</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1706,31 +1646,27 @@
         <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2">
-        <v>3</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">봉</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="J30" s="4"/>
       <c r="K30" s="2"/>
     </row>
     <row r="31">
@@ -1749,31 +1685,23 @@
         <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F31" s="2">
-        <v>3</v>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">황</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
     <row r="32">
@@ -1792,23 +1720,31 @@
         <v>3</v>
       </c>
       <c r="E32" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F32" s="2">
         <v>3</v>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="4"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢 위에 작은 ㅋ 모양 꾸밈(생략)</t>
+        </is>
+      </c>
       <c r="K32" s="2"/>
     </row>
     <row r="33">
@@ -1827,32 +1763,27 @@
         <v>3</v>
       </c>
       <c r="E33" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F33" s="2">
-        <v>4</v>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|潢</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵, 아래 ○</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">황</t>
+        </is>
+      </c>
+      <c r="J33" s="4"/>
       <c r="K33" s="2"/>
     </row>
     <row r="34">
@@ -1865,32 +1796,28 @@
         </is>
       </c>
       <c r="C34" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F34" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">만</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I34" s="2"/>
       <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
@@ -1904,37 +1831,34 @@
         </is>
       </c>
       <c r="C35" s="2">
+        <v>3</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3</v>
+      </c>
+      <c r="E35" s="2">
+        <v>10</v>
+      </c>
+      <c r="F35" s="2">
         <v>4</v>
       </c>
-      <c r="D35" s="2">
-        <v>4</v>
-      </c>
-      <c r="E35" s="2">
-        <v>2</v>
-      </c>
-      <c r="F35" s="2">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">수</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 요성</t>
-        </is>
-      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|㴌</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉황</t>
+        </is>
+      </c>
+      <c r="J35" s="4"/>
       <c r="K35" s="2"/>
     </row>
     <row r="36">
@@ -1947,30 +1871,31 @@
         </is>
       </c>
       <c r="C36" s="2">
+        <v>3</v>
+      </c>
+      <c r="D36" s="2">
+        <v>3</v>
+      </c>
+      <c r="E36" s="2">
+        <v>11</v>
+      </c>
+      <c r="F36" s="2">
         <v>4</v>
       </c>
-      <c r="D36" s="2">
-        <v>4</v>
-      </c>
-      <c r="E36" s="2">
-        <v>3</v>
-      </c>
-      <c r="F36" s="2">
-        <v>1</v>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">문</t>
+          <t xml:space="preserve">새어</t>
         </is>
       </c>
       <c r="J36" s="4"/>
@@ -1986,37 +1911,29 @@
         </is>
       </c>
       <c r="C37" s="2">
+        <v>3</v>
+      </c>
+      <c r="D37" s="2">
+        <v>3</v>
+      </c>
+      <c r="E37" s="2">
+        <v>12</v>
+      </c>
+      <c r="F37" s="2">
         <v>4</v>
       </c>
-      <c r="D37" s="2">
-        <v>4</v>
-      </c>
-      <c r="E37" s="2">
-        <v>4</v>
-      </c>
-      <c r="F37" s="2">
-        <v>2</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">新처럼 보이나 姑로 판독</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="4"/>
       <c r="K37" s="2"/>
     </row>
     <row r="38">
@@ -2035,23 +1952,31 @@
         <v>4</v>
       </c>
       <c r="E38" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2">
-        <v>2</v>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I38" s="2"/>
-      <c r="J38" s="4"/>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 안처럼 보임</t>
+        </is>
+      </c>
       <c r="K38" s="2"/>
     </row>
     <row r="39">
@@ -2070,228 +1995,225 @@
         <v>4</v>
       </c>
       <c r="E39" s="2">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수</t>
+        </is>
+      </c>
+      <c r="J39" s="4"/>
+      <c r="K39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C40" s="2">
+        <v>4</v>
+      </c>
+      <c r="D40" s="2">
+        <v>4</v>
+      </c>
+      <c r="E40" s="2">
+        <v>3</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>1</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C41" s="2">
+        <v>4</v>
+      </c>
+      <c r="D41" s="2">
+        <v>4</v>
+      </c>
+      <c r="E41" s="2">
+        <v>4</v>
+      </c>
+      <c r="F41" s="2">
+        <v>2</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문</t>
+        </is>
+      </c>
+      <c r="J41" s="4"/>
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C42" s="2">
+        <v>4</v>
+      </c>
+      <c r="D42" s="2">
+        <v>4</v>
+      </c>
+      <c r="E42" s="2">
+        <v>5</v>
+      </c>
+      <c r="F42" s="2">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|南</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전</t>
+        </is>
+      </c>
+      <c r="J42" s="4"/>
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>1</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C43" s="2">
+        <v>4</v>
+      </c>
+      <c r="D43" s="2">
+        <v>4</v>
+      </c>
+      <c r="E43" s="2">
         <v>6</v>
       </c>
-      <c r="F39" s="2">
-        <v>2</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="F43" s="2">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|無</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꾸</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵, 아래 無</t>
-        </is>
-      </c>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2">
-        <v>1</v>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C40" s="2">
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에에</t>
+        </is>
+      </c>
+      <c r="J43" s="4"/>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C44" s="2">
         <v>4</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D44" s="2">
         <v>4</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E44" s="2">
         <v>7</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F44" s="2">
         <v>3</v>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|無</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">웅</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵, 아래 無</t>
-        </is>
-      </c>
-      <c r="K40" s="2"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2">
-        <v>1</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C41" s="2">
-        <v>4</v>
-      </c>
-      <c r="D41" s="2">
-        <v>4</v>
-      </c>
-      <c r="E41" s="2">
-        <v>8</v>
-      </c>
-      <c r="F41" s="2">
-        <v>3</v>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변</t>
-        </is>
-      </c>
-      <c r="J41" s="4"/>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2">
-        <v>1</v>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C42" s="2">
-        <v>4</v>
-      </c>
-      <c r="D42" s="2">
-        <v>4</v>
-      </c>
-      <c r="E42" s="2">
-        <v>9</v>
-      </c>
-      <c r="F42" s="2">
-        <v>3</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I42" s="2"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2">
-        <v>1</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C43" s="2">
-        <v>4</v>
-      </c>
-      <c r="D43" s="2">
-        <v>4</v>
-      </c>
-      <c r="E43" s="2">
-        <v>12</v>
-      </c>
-      <c r="F43" s="2">
-        <v>4</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새</t>
-        </is>
-      </c>
-      <c r="J43" s="4"/>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2">
-        <v>1</v>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C44" s="2">
-        <v>5</v>
-      </c>
-      <c r="D44" s="2">
-        <v>5</v>
-      </c>
-      <c r="E44" s="2">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신</t>
-        </is>
-      </c>
-      <c r="J44" s="4"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구웅</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 구/푸?</t>
+        </is>
+      </c>
       <c r="K44" s="2"/>
     </row>
     <row r="45">
@@ -2304,16 +2226,16 @@
         </is>
       </c>
       <c r="C45" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F45" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -2327,12 +2249,12 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">고</t>
+          <t xml:space="preserve">년</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">氵? 요성</t>
+          <t xml:space="preserve">가사 변처럼 보임</t>
         </is>
       </c>
       <c r="K45" s="2"/>
@@ -2347,16 +2269,16 @@
         </is>
       </c>
       <c r="C46" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46" s="2">
+        <v>9</v>
+      </c>
+      <c r="F46" s="2">
         <v>3</v>
-      </c>
-      <c r="F46" s="2">
-        <v>1</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -2382,28 +2304,32 @@
         </is>
       </c>
       <c r="C47" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" s="2">
+        <v>10</v>
+      </c>
+      <c r="F47" s="2">
         <v>4</v>
       </c>
-      <c r="F47" s="2">
-        <v>2</v>
-      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南^</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I47" s="2"/>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새</t>
+        </is>
+      </c>
       <c r="J47" s="4"/>
       <c r="K47" s="2"/>
     </row>
@@ -2417,32 +2343,28 @@
         </is>
       </c>
       <c r="C48" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D48" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E48" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F48" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">성</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I48" s="2"/>
       <c r="J48" s="4"/>
       <c r="K48" s="2"/>
     </row>
@@ -2456,38 +2378,30 @@
         </is>
       </c>
       <c r="C49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F49" s="2">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|潢</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-潢</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무두</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 아래, 요성</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I49" s="2"/>
+      <c r="J49" s="4"/>
       <c r="K49" s="2"/>
     </row>
     <row r="50">
@@ -2506,320 +2420,299 @@
         <v>5</v>
       </c>
       <c r="E50" s="2">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 신처럼 보임</t>
+        </is>
+      </c>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>1</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C51" s="2">
+        <v>5</v>
+      </c>
+      <c r="D51" s="2">
+        <v>5</v>
+      </c>
+      <c r="E51" s="2">
+        <v>2</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="J51" s="4"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>1</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C52" s="2">
+        <v>5</v>
+      </c>
+      <c r="D52" s="2">
+        <v>5</v>
+      </c>
+      <c r="E52" s="2">
+        <v>3</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I52" s="2"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>1</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C53" s="2">
+        <v>5</v>
+      </c>
+      <c r="D53" s="2">
+        <v>5</v>
+      </c>
+      <c r="E53" s="2">
+        <v>4</v>
+      </c>
+      <c r="F53" s="2">
+        <v>2</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">곡</t>
+        </is>
+      </c>
+      <c r="J53" s="4"/>
+      <c r="K53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>1</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C54" s="2">
+        <v>5</v>
+      </c>
+      <c r="D54" s="2">
+        <v>5</v>
+      </c>
+      <c r="E54" s="2">
+        <v>5</v>
+      </c>
+      <c r="F54" s="2">
+        <v>2</v>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">심</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 성처럼 보임</t>
+        </is>
+      </c>
+      <c r="K54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>1</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C55" s="2">
+        <v>5</v>
+      </c>
+      <c r="D55" s="2">
+        <v>5</v>
+      </c>
+      <c r="E55" s="2">
+        <v>6</v>
+      </c>
+      <c r="F55" s="2">
+        <v>2</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>1</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C56" s="2">
+        <v>5</v>
+      </c>
+      <c r="D56" s="2">
+        <v>5</v>
+      </c>
+      <c r="E56" s="2">
+        <v>7</v>
+      </c>
+      <c r="F56" s="2">
+        <v>3</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|㴌</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+㴌</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무우</t>
+        </is>
+      </c>
+      <c r="J56" s="4"/>
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>1</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C57" s="2">
+        <v>5</v>
+      </c>
+      <c r="D57" s="2">
+        <v>5</v>
+      </c>
+      <c r="E57" s="2">
         <v>8</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F57" s="2">
         <v>3</v>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|無</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">이인</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵, 아래 無</t>
-        </is>
-      </c>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2">
-        <v>1</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C51" s="2">
-        <v>5</v>
-      </c>
-      <c r="D51" s="2">
-        <v>5</v>
-      </c>
-      <c r="E51" s="2">
-        <v>9</v>
-      </c>
-      <c r="F51" s="2">
-        <v>3</v>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I51" s="2"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2">
-        <v>1</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C52" s="2">
-        <v>5</v>
-      </c>
-      <c r="D52" s="2">
-        <v>5</v>
-      </c>
-      <c r="E52" s="2">
-        <v>12</v>
-      </c>
-      <c r="F52" s="2">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">초</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵</t>
-        </is>
-      </c>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2">
-        <v>1</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C53" s="2">
-        <v>6</v>
-      </c>
-      <c r="D53" s="2">
-        <v>6</v>
-      </c>
-      <c r="E53" s="2">
-        <v>1</v>
-      </c>
-      <c r="F53" s="2">
-        <v>1</v>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|潢</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-潢</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 潢(氵)</t>
-        </is>
-      </c>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2">
-        <v>1</v>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C54" s="2">
-        <v>6</v>
-      </c>
-      <c r="D54" s="2">
-        <v>6</v>
-      </c>
-      <c r="E54" s="2">
-        <v>2</v>
-      </c>
-      <c r="F54" s="2">
-        <v>1</v>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|黃</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-黃</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흔</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵, 긴 사선 꾸밈</t>
-        </is>
-      </c>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2">
-        <v>1</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C55" s="2">
-        <v>6</v>
-      </c>
-      <c r="D55" s="2">
-        <v>6</v>
-      </c>
-      <c r="E55" s="2">
-        <v>3</v>
-      </c>
-      <c r="F55" s="2">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">긴 사선(요성) 꾸밈 아래 公 비슷한 기호, 판독 불명; 가사 화</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2">
-        <v>1</v>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C56" s="2">
-        <v>6</v>
-      </c>
-      <c r="D56" s="2">
-        <v>6</v>
-      </c>
-      <c r="E56" s="2">
-        <v>4</v>
-      </c>
-      <c r="F56" s="2">
-        <v>2</v>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">답</t>
-        </is>
-      </c>
-      <c r="J56" s="4"/>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2">
-        <v>1</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C57" s="2">
-        <v>6</v>
-      </c>
-      <c r="D57" s="2">
-        <v>6</v>
-      </c>
-      <c r="E57" s="2">
-        <v>5</v>
-      </c>
-      <c r="F57" s="2">
-        <v>2</v>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J57" s="4"/>
@@ -2835,194 +2728,191 @@
         </is>
       </c>
       <c r="C58" s="2">
+        <v>5</v>
+      </c>
+      <c r="D58" s="2">
+        <v>5</v>
+      </c>
+      <c r="E58" s="2">
+        <v>9</v>
+      </c>
+      <c r="F58" s="2">
+        <v>3</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I58" s="2"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>1</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C59" s="2">
+        <v>5</v>
+      </c>
+      <c r="D59" s="2">
+        <v>5</v>
+      </c>
+      <c r="E59" s="2">
+        <v>10</v>
+      </c>
+      <c r="F59" s="2">
+        <v>4</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초</t>
+        </is>
+      </c>
+      <c r="J59" s="4"/>
+      <c r="K59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>1</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C60" s="2">
+        <v>5</v>
+      </c>
+      <c r="D60" s="2">
+        <v>5</v>
+      </c>
+      <c r="E60" s="2">
+        <v>11</v>
+      </c>
+      <c r="F60" s="2">
+        <v>4</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
+      <c r="J60" s="4"/>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>1</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C61" s="2">
         <v>6</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D61" s="2">
         <v>6</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E61" s="2">
+        <v>1</v>
+      </c>
+      <c r="F61" s="2">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|㴌</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+㴌</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우을</t>
+        </is>
+      </c>
+      <c r="J61" s="4"/>
+      <c r="K61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <v>1</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C62" s="2">
         <v>6</v>
       </c>
-      <c r="F58" s="2">
-        <v>2</v>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="D62" s="2">
+        <v>6</v>
+      </c>
+      <c r="E62" s="2">
+        <v>2</v>
+      </c>
+      <c r="F62" s="2">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|無</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">쪼오</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵, 아래 無; 가사 조오?</t>
-        </is>
-      </c>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2">
-        <v>1</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C59" s="2">
-        <v>6</v>
-      </c>
-      <c r="D59" s="2">
-        <v>6</v>
-      </c>
-      <c r="E59" s="2">
-        <v>7</v>
-      </c>
-      <c r="F59" s="2">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">뭇</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵</t>
-        </is>
-      </c>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2">
-        <v>1</v>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C60" s="2">
-        <v>6</v>
-      </c>
-      <c r="D60" s="2">
-        <v>6</v>
-      </c>
-      <c r="E60" s="2">
-        <v>8</v>
-      </c>
-      <c r="F60" s="2">
-        <v>3</v>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새</t>
-        </is>
-      </c>
-      <c r="J60" s="4"/>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2">
-        <v>1</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C61" s="2">
-        <v>6</v>
-      </c>
-      <c r="D61" s="2">
-        <v>6</v>
-      </c>
-      <c r="E61" s="2">
-        <v>9</v>
-      </c>
-      <c r="F61" s="2">
-        <v>3</v>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">든</t>
-        </is>
-      </c>
-      <c r="J61" s="4"/>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2">
-        <v>1</v>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C62" s="2">
-        <v>6</v>
-      </c>
-      <c r="D62" s="2">
-        <v>6</v>
-      </c>
-      <c r="E62" s="2">
-        <v>10</v>
-      </c>
-      <c r="F62" s="2">
-        <v>4</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I62" s="2"/>
-      <c r="J62" s="4"/>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리임</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">긴 곡선이 3정간까지 이어짐</t>
+        </is>
+      </c>
       <c r="K62" s="2"/>
     </row>
     <row r="63">
@@ -3041,31 +2931,23 @@
         <v>6</v>
       </c>
       <c r="E63" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F63" s="2">
-        <v>4</v>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 ○</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I63" s="2"/>
+      <c r="J63" s="4"/>
       <c r="K63" s="2"/>
     </row>
     <row r="64">
@@ -3078,38 +2960,33 @@
         </is>
       </c>
       <c r="C64" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D64" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E64" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" s="2">
-        <v>1</v>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|黃</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-黃</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우을</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵; 가사 우을리임이 1~2정간 걸침</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비</t>
+        </is>
+      </c>
+      <c r="J64" s="4"/>
       <c r="K64" s="2"/>
     </row>
     <row r="65">
@@ -3122,38 +2999,29 @@
         </is>
       </c>
       <c r="C65" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D65" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E65" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F65" s="2">
-        <v>1</v>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|黃</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-黃</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리임</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I65" s="2"/>
+      <c r="J65" s="4"/>
       <c r="K65" s="2"/>
     </row>
     <row r="66">
@@ -3166,28 +3034,33 @@
         </is>
       </c>
       <c r="C66" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D66" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F66" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I66" s="2"/>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조오</t>
+        </is>
+      </c>
       <c r="J66" s="4"/>
       <c r="K66" s="2"/>
     </row>
@@ -3201,38 +3074,33 @@
         </is>
       </c>
       <c r="C67" s="2">
+        <v>6</v>
+      </c>
+      <c r="D67" s="2">
+        <v>6</v>
+      </c>
+      <c r="E67" s="2">
         <v>7</v>
       </c>
-      <c r="D67" s="2">
-        <v>7</v>
-      </c>
-      <c r="E67" s="2">
-        <v>4</v>
-      </c>
       <c r="F67" s="2">
-        <v>2</v>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|潢</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵, 두 글자 겹침</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뭇</t>
+        </is>
+      </c>
+      <c r="J67" s="4"/>
       <c r="K67" s="2"/>
     </row>
     <row r="68">
@@ -3245,28 +3113,32 @@
         </is>
       </c>
       <c r="C68" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D68" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E68" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F68" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南^</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I68" s="2"/>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새</t>
+        </is>
+      </c>
       <c r="J68" s="4"/>
       <c r="K68" s="2"/>
     </row>
@@ -3280,28 +3152,32 @@
         </is>
       </c>
       <c r="C69" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E69" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F69" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">南^</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I69" s="2"/>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들</t>
+        </is>
+      </c>
       <c r="J69" s="4"/>
       <c r="K69" s="2"/>
     </row>
@@ -3315,34 +3191,33 @@
         </is>
       </c>
       <c r="C70" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D70" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E70" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F70" s="2">
-        <v>3</v>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I70" s="3"/>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵, 아래 無</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="J70" s="4"/>
       <c r="K70" s="2"/>
     </row>
     <row r="71">
@@ -3355,25 +3230,25 @@
         </is>
       </c>
       <c r="C71" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D71" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E71" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F71" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I71" s="2"/>
@@ -3390,25 +3265,26 @@
         </is>
       </c>
       <c r="C72" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D72" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E72" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F72" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I72" s="2"/>
@@ -3431,31 +3307,27 @@
         <v>7</v>
       </c>
       <c r="E73" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F73" s="2">
-        <v>4</v>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">초</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 ○</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농</t>
+        </is>
+      </c>
+      <c r="J73" s="4"/>
       <c r="K73" s="2"/>
     </row>
     <row r="74">
@@ -3468,33 +3340,37 @@
         </is>
       </c>
       <c r="C74" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E74" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="2">
         <v>1</v>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">쌍</t>
-        </is>
-      </c>
-      <c r="J74" s="4"/>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">춘</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 춘/촌?</t>
+        </is>
+      </c>
       <c r="K74" s="2"/>
     </row>
     <row r="75">
@@ -3507,13 +3383,13 @@
         </is>
       </c>
       <c r="C75" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D75" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E75" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F75" s="2">
         <v>1</v>
@@ -3542,38 +3418,34 @@
         </is>
       </c>
       <c r="C76" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D76" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E76" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="2">
-        <v>1</v>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|黃</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-黃</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">거어</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵; 가사 거어</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|㴌</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+㴌</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화답</t>
+        </is>
+      </c>
+      <c r="J76" s="4"/>
       <c r="K76" s="2"/>
     </row>
     <row r="77">
@@ -3586,37 +3458,33 @@
         </is>
       </c>
       <c r="C77" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D77" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E77" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F77" s="2">
         <v>2</v>
       </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">쌍</t>
-        </is>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵</t>
-        </is>
-      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J77" s="4"/>
       <c r="K77" s="2"/>
     </row>
     <row r="78">
@@ -3629,32 +3497,28 @@
         </is>
       </c>
       <c r="C78" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D78" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E78" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F78" s="2">
         <v>2</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">러</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I78" s="2"/>
       <c r="J78" s="4"/>
       <c r="K78" s="2"/>
     </row>
@@ -3668,30 +3532,31 @@
         </is>
       </c>
       <c r="C79" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D79" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E79" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F79" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">데</t>
+          <t xml:space="preserve">짝악</t>
         </is>
       </c>
       <c r="J79" s="4"/>
@@ -3707,72 +3572,72 @@
         </is>
       </c>
       <c r="C80" s="2">
+        <v>7</v>
+      </c>
+      <c r="D80" s="2">
+        <v>7</v>
+      </c>
+      <c r="E80" s="2">
         <v>8</v>
-      </c>
-      <c r="D80" s="2">
-        <v>8</v>
-      </c>
-      <c r="E80" s="2">
-        <v>7</v>
       </c>
       <c r="F80" s="2">
         <v>3</v>
       </c>
-      <c r="G80" s="3" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="J80" s="4"/>
+      <c r="K80" s="2"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2">
+        <v>1</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C81" s="2">
+        <v>7</v>
+      </c>
+      <c r="D81" s="2">
+        <v>7</v>
+      </c>
+      <c r="E81" s="2">
+        <v>9</v>
+      </c>
+      <c r="F81" s="2">
+        <v>3</v>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|無</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">날아</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵, 아래 無</t>
-        </is>
-      </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2">
-        <v>1</v>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C81" s="2">
-        <v>8</v>
-      </c>
-      <c r="D81" s="2">
-        <v>8</v>
-      </c>
-      <c r="E81" s="2">
-        <v>8</v>
-      </c>
-      <c r="F81" s="2">
-        <v>3</v>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I81" s="2"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지어</t>
+        </is>
+      </c>
       <c r="J81" s="4"/>
       <c r="K81" s="2"/>
     </row>
@@ -3786,28 +3651,32 @@
         </is>
       </c>
       <c r="C82" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D82" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E82" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I82" s="2"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
       <c r="J82" s="4"/>
       <c r="K82" s="2"/>
     </row>
@@ -3821,37 +3690,29 @@
         </is>
       </c>
       <c r="C83" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D83" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E83" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F83" s="2">
         <v>4</v>
       </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">든</t>
-        </is>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 ○</t>
-        </is>
-      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I83" s="2"/>
+      <c r="J83" s="4"/>
       <c r="K83" s="2"/>
     </row>
     <row r="84">
@@ -3864,32 +3725,29 @@
         </is>
       </c>
       <c r="C84" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D84" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E84" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F84" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I84" s="2"/>
       <c r="J84" s="4"/>
       <c r="K84" s="2"/>
     </row>
@@ -3903,37 +3761,33 @@
         </is>
       </c>
       <c r="C85" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D85" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E85" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F85" s="2">
-        <v>2</v>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꾹</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 꾹 꾸밈</t>
-        </is>
-      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쌍</t>
+        </is>
+      </c>
+      <c r="J85" s="4"/>
       <c r="K85" s="2"/>
     </row>
     <row r="86">
@@ -3946,32 +3800,28 @@
         </is>
       </c>
       <c r="C86" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D86" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E86" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F86" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I86" s="2"/>
       <c r="J86" s="4"/>
       <c r="K86" s="2"/>
     </row>
@@ -3985,30 +3835,31 @@
         </is>
       </c>
       <c r="C87" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D87" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E87" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F87" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가</t>
+          <t xml:space="preserve">거어</t>
         </is>
       </c>
       <c r="J87" s="4"/>
@@ -4024,155 +3875,156 @@
         </is>
       </c>
       <c r="C88" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D88" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E88" s="2">
+        <v>4</v>
+      </c>
+      <c r="F88" s="2">
+        <v>2</v>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쌍</t>
+        </is>
+      </c>
+      <c r="J88" s="4"/>
+      <c r="K88" s="2"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2">
+        <v>1</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C89" s="2">
+        <v>8</v>
+      </c>
+      <c r="D89" s="2">
+        <v>8</v>
+      </c>
+      <c r="E89" s="2">
+        <v>5</v>
+      </c>
+      <c r="F89" s="2">
+        <v>2</v>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">래</t>
+        </is>
+      </c>
+      <c r="J89" s="4"/>
+      <c r="K89" s="2"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2">
+        <v>1</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C90" s="2">
+        <v>8</v>
+      </c>
+      <c r="D90" s="2">
+        <v>8</v>
+      </c>
+      <c r="E90" s="2">
+        <v>6</v>
+      </c>
+      <c r="F90" s="2">
+        <v>2</v>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|南</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 베/비?</t>
+        </is>
+      </c>
+      <c r="K90" s="2"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2">
+        <v>1</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C91" s="2">
+        <v>8</v>
+      </c>
+      <c r="D91" s="2">
+        <v>8</v>
+      </c>
+      <c r="E91" s="2">
         <v>7</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F91" s="2">
         <v>3</v>
       </c>
-      <c r="G88" s="3" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|無</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을우ㅁ</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵, 아래 無; 가사 을움?</t>
-        </is>
-      </c>
-      <c r="K88" s="2"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2">
-        <v>1</v>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C89" s="2">
-        <v>9</v>
-      </c>
-      <c r="D89" s="2">
-        <v>9</v>
-      </c>
-      <c r="E89" s="2">
-        <v>8</v>
-      </c>
-      <c r="F89" s="2">
-        <v>3</v>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">윤</t>
-        </is>
-      </c>
-      <c r="J89" s="4"/>
-      <c r="K89" s="2"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2">
-        <v>1</v>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C90" s="2">
-        <v>9</v>
-      </c>
-      <c r="D90" s="2">
-        <v>9</v>
-      </c>
-      <c r="E90" s="2">
-        <v>9</v>
-      </c>
-      <c r="F90" s="2">
-        <v>3</v>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I90" s="2"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="2"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2">
-        <v>1</v>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/새 타령.png</t>
-        </is>
-      </c>
-      <c r="C91" s="2">
-        <v>9</v>
-      </c>
-      <c r="D91" s="2">
-        <v>9</v>
-      </c>
-      <c r="E91" s="2">
-        <v>12</v>
-      </c>
-      <c r="F91" s="2">
-        <v>4</v>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아래 요성</t>
-        </is>
-      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">날아</t>
+        </is>
+      </c>
+      <c r="J91" s="4"/>
       <c r="K91" s="2"/>
     </row>
     <row r="92">
@@ -4185,38 +4037,29 @@
         </is>
       </c>
       <c r="C92" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D92" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E92" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F92" s="2">
-        <v>1</v>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|潢</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-潢</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우을</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간1 南 아래 潢(氵)</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I92" s="2"/>
+      <c r="J92" s="4"/>
       <c r="K92" s="2"/>
     </row>
     <row r="93">
@@ -4229,37 +4072,29 @@
         </is>
       </c>
       <c r="C93" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D93" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E93" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F93" s="2">
-        <v>1</v>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I93" s="2"/>
+      <c r="J93" s="4"/>
       <c r="K93" s="2"/>
     </row>
     <row r="94">
@@ -4272,28 +4107,32 @@
         </is>
       </c>
       <c r="C94" s="2">
+        <v>8</v>
+      </c>
+      <c r="D94" s="2">
+        <v>8</v>
+      </c>
+      <c r="E94" s="2">
         <v>10</v>
       </c>
-      <c r="D94" s="2">
-        <v>10</v>
-      </c>
-      <c r="E94" s="2">
-        <v>3</v>
-      </c>
       <c r="F94" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I94" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">든</t>
+        </is>
+      </c>
       <c r="J94" s="4"/>
       <c r="K94" s="2"/>
     </row>
@@ -4307,28 +4146,32 @@
         </is>
       </c>
       <c r="C95" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D95" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E95" s="2">
+        <v>11</v>
+      </c>
+      <c r="F95" s="2">
         <v>4</v>
       </c>
-      <c r="F95" s="2">
-        <v>2</v>
-      </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I95" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="J95" s="4"/>
       <c r="K95" s="2"/>
     </row>
@@ -4342,25 +4185,26 @@
         </is>
       </c>
       <c r="C96" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D96" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E96" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F96" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I96" s="2"/>
@@ -4377,28 +4221,32 @@
         </is>
       </c>
       <c r="C97" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E97" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F97" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I97" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저</t>
+        </is>
+      </c>
       <c r="J97" s="4"/>
       <c r="K97" s="2"/>
     </row>
@@ -4412,42 +4260,720 @@
         </is>
       </c>
       <c r="C98" s="2">
+        <v>9</v>
+      </c>
+      <c r="D98" s="2">
+        <v>9</v>
+      </c>
+      <c r="E98" s="2">
+        <v>2</v>
+      </c>
+      <c r="F98" s="2">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I98" s="2"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="2"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2">
+        <v>1</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C99" s="2">
+        <v>9</v>
+      </c>
+      <c r="D99" s="2">
+        <v>9</v>
+      </c>
+      <c r="E99" s="2">
+        <v>3</v>
+      </c>
+      <c r="F99" s="2">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쑥</t>
+        </is>
+      </c>
+      <c r="J99" s="4"/>
+      <c r="K99" s="2"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2">
+        <v>1</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C100" s="2">
+        <v>9</v>
+      </c>
+      <c r="D100" s="2">
+        <v>9</v>
+      </c>
+      <c r="E100" s="2">
+        <v>4</v>
+      </c>
+      <c r="F100" s="2">
+        <v>2</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꾹</t>
+        </is>
+      </c>
+      <c r="J100" s="4"/>
+      <c r="K100" s="2"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2">
+        <v>1</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C101" s="2">
+        <v>9</v>
+      </c>
+      <c r="D101" s="2">
+        <v>9</v>
+      </c>
+      <c r="E101" s="2">
+        <v>5</v>
+      </c>
+      <c r="F101" s="2">
+        <v>2</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새</t>
+        </is>
+      </c>
+      <c r="J101" s="4"/>
+      <c r="K101" s="2"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2">
+        <v>1</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C102" s="2">
+        <v>9</v>
+      </c>
+      <c r="D102" s="2">
+        <v>9</v>
+      </c>
+      <c r="E102" s="2">
+        <v>6</v>
+      </c>
+      <c r="F102" s="2">
+        <v>2</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="J102" s="4"/>
+      <c r="K102" s="2"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2">
+        <v>1</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C103" s="2">
+        <v>9</v>
+      </c>
+      <c r="D103" s="2">
+        <v>9</v>
+      </c>
+      <c r="E103" s="2">
+        <v>7</v>
+      </c>
+      <c r="F103" s="2">
+        <v>3</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|無</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">울음</t>
+        </is>
+      </c>
+      <c r="J103" s="4"/>
+      <c r="K103" s="2"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2">
+        <v>1</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C104" s="2">
+        <v>9</v>
+      </c>
+      <c r="D104" s="2">
+        <v>9</v>
+      </c>
+      <c r="E104" s="2">
+        <v>8</v>
+      </c>
+      <c r="F104" s="2">
+        <v>3</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">운</t>
+        </is>
+      </c>
+      <c r="J104" s="4"/>
+      <c r="K104" s="2"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2">
+        <v>1</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C105" s="2">
+        <v>9</v>
+      </c>
+      <c r="D105" s="2">
+        <v>9</v>
+      </c>
+      <c r="E105" s="2">
+        <v>9</v>
+      </c>
+      <c r="F105" s="2">
+        <v>3</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I105" s="2"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="2"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2">
+        <v>1</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C106" s="2">
+        <v>9</v>
+      </c>
+      <c r="D106" s="2">
+        <v>9</v>
+      </c>
+      <c r="E106" s="2">
         <v>10</v>
       </c>
-      <c r="D98" s="2">
+      <c r="F106" s="2">
+        <v>4</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="J106" s="4"/>
+      <c r="K106" s="2"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2">
+        <v>1</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C107" s="2">
+        <v>9</v>
+      </c>
+      <c r="D107" s="2">
+        <v>9</v>
+      </c>
+      <c r="E107" s="2">
+        <v>11</v>
+      </c>
+      <c r="F107" s="2">
+        <v>4</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J107" s="4"/>
+      <c r="K107" s="2"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2">
+        <v>1</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C108" s="2">
         <v>10</v>
       </c>
-      <c r="E98" s="2">
+      <c r="D108" s="2">
+        <v>10</v>
+      </c>
+      <c r="E108" s="2">
+        <v>1</v>
+      </c>
+      <c r="F108" s="2">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|㴌</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+㴌</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우을</t>
+        </is>
+      </c>
+      <c r="J108" s="4"/>
+      <c r="K108" s="2"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2">
+        <v>1</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C109" s="2">
+        <v>10</v>
+      </c>
+      <c r="D109" s="2">
+        <v>10</v>
+      </c>
+      <c r="E109" s="2">
+        <v>2</v>
+      </c>
+      <c r="F109" s="2">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J109" s="4"/>
+      <c r="K109" s="2"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2">
+        <v>1</v>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C110" s="2">
+        <v>10</v>
+      </c>
+      <c r="D110" s="2">
+        <v>10</v>
+      </c>
+      <c r="E110" s="2">
+        <v>3</v>
+      </c>
+      <c r="F110" s="2">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I110" s="2"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="2"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2">
+        <v>1</v>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C111" s="2">
+        <v>10</v>
+      </c>
+      <c r="D111" s="2">
+        <v>10</v>
+      </c>
+      <c r="E111" s="2">
+        <v>4</v>
+      </c>
+      <c r="F111" s="2">
+        <v>2</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I111" s="2"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="2"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2">
+        <v>1</v>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C112" s="2">
+        <v>10</v>
+      </c>
+      <c r="D112" s="2">
+        <v>10</v>
+      </c>
+      <c r="E112" s="2">
+        <v>5</v>
+      </c>
+      <c r="F112" s="2">
+        <v>2</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I112" s="2"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="2"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2">
+        <v>1</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C113" s="2">
+        <v>10</v>
+      </c>
+      <c r="D113" s="2">
+        <v>10</v>
+      </c>
+      <c r="E113" s="2">
+        <v>6</v>
+      </c>
+      <c r="F113" s="2">
+        <v>2</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I113" s="2"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="2"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2">
+        <v>1</v>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C114" s="2">
+        <v>10</v>
+      </c>
+      <c r="D114" s="2">
+        <v>10</v>
+      </c>
+      <c r="E114" s="2">
+        <v>10</v>
+      </c>
+      <c r="F114" s="2">
+        <v>4</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|㴌</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어어</t>
+        </is>
+      </c>
+      <c r="J114" s="4"/>
+      <c r="K114" s="2"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2">
+        <v>1</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C115" s="2">
+        <v>10</v>
+      </c>
+      <c r="D115" s="2">
+        <v>10</v>
+      </c>
+      <c r="E115" s="2">
+        <v>11</v>
+      </c>
+      <c r="F115" s="2">
+        <v>4</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|無</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어어</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">○로 묶음(생략)</t>
+        </is>
+      </c>
+      <c r="K115" s="2"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2">
+        <v>1</v>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/새 타령.png</t>
+        </is>
+      </c>
+      <c r="C116" s="2">
+        <v>10</v>
+      </c>
+      <c r="D116" s="2">
+        <v>10</v>
+      </c>
+      <c r="E116" s="2">
         <v>12</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F116" s="2">
         <v>4</v>
       </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|潢</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어어</t>
-        </is>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵, ○로 묶음(黃無 겹침)</t>
-        </is>
-      </c>
-      <c r="K98" s="2"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I116" s="2"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K98"/>
+  <autoFilter ref="A1:K116"/>
 </worksheet>
 </file>
 
@@ -4480,7 +5006,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4507,563 +5033,587 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-潢</t>
-        </is>
-      </c>
-      <c r="C3" s="31" t="inlineStr">
+㴌</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 을</t>
         </is>
       </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="32" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쌍</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-黃</t>
-        </is>
-      </c>
-      <c r="I3" s="31" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+㴌</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 을</t>
         </is>
       </c>
-      <c r="J3" s="21" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산</t>
+        </is>
+      </c>
+      <c r="N3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만</t>
+        </is>
+      </c>
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-潢</t>
-        </is>
-      </c>
-      <c r="K3" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농</t>
-        </is>
-      </c>
-      <c r="L3" s="23" t="inlineStr">
+–㴌</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새
+에</t>
+        </is>
+      </c>
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신</t>
-        </is>
-      </c>
-      <c r="N3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O3" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">만</t>
-        </is>
-      </c>
-      <c r="P3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q3" s="31" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">온</t>
+        </is>
+      </c>
+      <c r="T3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="R3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="S3" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">온</t>
-        </is>
-      </c>
-      <c r="T3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U3" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
+    </row>
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I4" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">춘</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-黃</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="inlineStr">
+無</t>
+        </is>
+      </c>
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리
 임</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수</t>
+        </is>
+      </c>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S4" s="25"/>
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U4" s="25"/>
+    </row>
+    <row r="5" ht="52.21" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쑥</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-黃</t>
-        </is>
-      </c>
-      <c r="K4" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흔</t>
-        </is>
-      </c>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M4" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O4" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">수</t>
-        </is>
-      </c>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S4" s="34"/>
-      <c r="T4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="U4" s="34"/>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E5" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저</t>
-        </is>
-      </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-黃</t>
-        </is>
-      </c>
-      <c r="G5" s="36" t="inlineStr">
+無</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">거
 어</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I5" s="35"/>
-      <c r="J5" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="K5" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화</t>
-        </is>
-      </c>
-      <c r="L5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M5" s="35"/>
-      <c r="N5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O5" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문</t>
-        </is>
-      </c>
-      <c r="P5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q5" s="35"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I5" s="27"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="K5" s="27"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M5" s="27"/>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O5" s="27"/>
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q5" s="27"/>
       <c r="R5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃
-無</t>
-        </is>
-      </c>
-      <c r="S5" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">갓</t>
-        </is>
-      </c>
-      <c r="T5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="U5" s="35"/>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꾹</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G6" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">쌍</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="I6" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
-        </is>
-      </c>
-      <c r="J6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K6" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">답</t>
-        </is>
-      </c>
-      <c r="L6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M6" s="32"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O6" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전</t>
-        </is>
-      </c>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q6" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="R6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S6" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잡</t>
-        </is>
-      </c>
-      <c r="T6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U6" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E7" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G7" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">러</t>
-        </is>
-      </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I7" s="34"/>
-      <c r="J7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K7" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="L7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M7" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">성</t>
-        </is>
-      </c>
-      <c r="N7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O7" s="34"/>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q7" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S7" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새</t>
-        </is>
-      </c>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="U7" s="34"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E8" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G8" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">데</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I8" s="35"/>
-      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K8" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">쪼
-오</t>
-        </is>
-      </c>
-      <c r="L8" s="23"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="21" t="inlineStr">
+      <c r="S5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">갓</t>
+        </is>
+      </c>
+      <c r="T5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U5" s="27"/>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꾹</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쌍</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+㴌</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화
+답</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">곡</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잡</t>
+        </is>
+      </c>
+      <c r="T6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52.21" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">래</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K7" s="25"/>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">심</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="Q7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="R7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새</t>
+        </is>
+      </c>
+      <c r="T7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U7" s="25"/>
+    </row>
+    <row r="8" ht="52.21" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I8" s="27"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O8" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꾸</t>
-        </is>
-      </c>
-      <c r="P8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q8" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="R8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S8" s="35"/>
-      <c r="T8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="U8" s="35"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="K8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조
+오</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M8" s="27"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을
-우
-ㅁ</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="O8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에
+에</t>
+        </is>
+      </c>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="S8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="T8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U8" s="27"/>
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G9" s="31" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">울
+음</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">날
 아</t>
@@ -5075,13 +5625,18 @@
 無</t>
         </is>
       </c>
-      <c r="I9" s="31"/>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짝
+악</t>
+        </is>
+      </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K9" s="31" t="inlineStr">
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">뭇</t>
         </is>
@@ -5089,93 +5644,98 @@
       <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-潢</t>
-        </is>
-      </c>
-      <c r="M9" s="31" t="inlineStr">
+㴌</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">무
-두</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
+우</t>
+        </is>
+      </c>
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O9" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">웅</t>
-        </is>
-      </c>
-      <c r="P9" s="21" t="inlineStr">
+      <c r="O9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구
+웅</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="31" t="inlineStr">
+      <c r="Q9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">봉</t>
         </is>
       </c>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-南</t>
-        </is>
-      </c>
-      <c r="S9" s="32" t="inlineStr">
+無</t>
+        </is>
+      </c>
+      <c r="S9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">날
 아</t>
         </is>
       </c>
-      <c r="T9" s="23" t="inlineStr">
+      <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-南</t>
-        </is>
-      </c>
-      <c r="U9" s="32" t="inlineStr">
+無</t>
+        </is>
+      </c>
+      <c r="U9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">날
 아</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="55.19" customHeight="1">
+    <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="B10" s="21"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">윤</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">운</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G10" s="34"/>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I10" s="34"/>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K10" s="34" t="inlineStr">
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -5186,7 +5746,7 @@
 無</t>
         </is>
       </c>
-      <c r="M10" s="33" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 인</t>
@@ -5197,268 +5757,374 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O10" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">변</t>
+      <c r="O10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">년</t>
         </is>
       </c>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q10" s="33" t="inlineStr">
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">황</t>
         </is>
       </c>
-      <c r="R10" s="23" t="inlineStr">
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S10" s="34" t="inlineStr">
+      <c r="S10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
       </c>
-      <c r="T10" s="23" t="inlineStr">
+      <c r="T10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U10" s="34" t="inlineStr">
+      <c r="U10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="55.19" customHeight="1">
+    <row r="11" ht="52.21" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G11" s="35"/>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I11" s="35"/>
-      <c r="J11" s="23" t="inlineStr">
+      <c r="B11" s="21"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E11" s="27"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지
+어</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="K11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M11" s="27"/>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O11" s="27"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="S11" s="27"/>
+      <c r="T11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="U11" s="27"/>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
+      <c r="A12" s="0"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+어</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">든</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봉
+황</t>
+        </is>
+      </c>
+      <c r="R12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="T12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+어</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K11" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">든</t>
-        </is>
-      </c>
-      <c r="L11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M11" s="35"/>
-      <c r="N11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O11" s="35"/>
-      <c r="P11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S11" s="35"/>
-      <c r="T11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="U11" s="35"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K12" s="32"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="32"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="S12" s="32"/>
-      <c r="T12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="U12" s="32"/>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="34"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O13" s="25"/>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="Q13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새
+어</t>
+        </is>
+      </c>
+      <c r="R13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="S13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="T13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어
-어</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E14" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="27"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G14" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">든</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="27"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I14" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">초</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I14" s="27"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K14" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M14" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">초</t>
-        </is>
-      </c>
-      <c r="N14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O14" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K14" s="27"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="O14" s="27"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="Q14" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="Q14" s="27"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S14" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="S14" s="27"/>
       <c r="T14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U14" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="U14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/새 타령.xlsx
+++ b/sheets/민요/검수/새 타령.xlsx
@@ -605,10 +605,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/새 타령.xlsx
+++ b/sheets/민요/검수/새 타령.xlsx
@@ -506,24 +506,8 @@
 황</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
+    <t xml:space="preserve">潢
+無</t>
   </si>
   <si>
     <t xml:space="preserve">새
@@ -546,17 +530,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -678,7 +662,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -736,6 +720,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4707,704 +4735,704 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:U14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="S3" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="T3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U3" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="9" t="s">
+      <c r="D4" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="22"/>
+      <c r="H4" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="R4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="S4" s="11"/>
-      <c r="T4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="U4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="7" t="s">
+      <c r="R4" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" s="22"/>
+      <c r="T4" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="U4" s="22"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B5" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="7" t="s">
+      <c r="H5" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="24"/>
+      <c r="J5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="7" t="s">
+      <c r="K5" s="24"/>
+      <c r="L5" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="24"/>
+      <c r="N5" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" s="24"/>
+      <c r="P5" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="S5" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="T5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="U5" s="13"/>
-    </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="7" t="s">
+      <c r="T5" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="U5" s="24"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B6" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="Q6" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="R6" s="7" t="s">
+      <c r="R6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="S6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="T6" s="7" t="s">
+      <c r="T6" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="U6" s="8" t="s">
+      <c r="U6" s="19" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B7" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="9" t="s">
+      <c r="J7" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="22"/>
+      <c r="L7" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="R7" s="7" t="s">
+      <c r="R7" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="S7" s="11" t="s">
+      <c r="S7" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="T7" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="U7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="7" t="s">
+      <c r="T7" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="U7" s="22"/>
+    </row>
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B8" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="7" t="s">
+      <c r="H8" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="24"/>
+      <c r="J8" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="7" t="s">
+      <c r="L8" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="24"/>
+      <c r="N8" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="O8" s="13" t="s">
+      <c r="O8" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="P8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="7" t="s">
+      <c r="P8" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="S8" s="13" t="s">
+      <c r="S8" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="T8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="U8" s="13"/>
-    </row>
-    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="7" t="s">
+      <c r="T8" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="U8" s="24"/>
+    </row>
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B9" s="18"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="N9" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="P9" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="Q9" s="10" t="s">
+      <c r="Q9" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="R9" s="7" t="s">
+      <c r="R9" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="S9" s="8" t="s">
+      <c r="S9" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="T9" s="7" t="s">
+      <c r="T9" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="U9" s="8" t="s">
+      <c r="U9" s="19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B10" s="18"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="22"/>
+      <c r="H10" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="N10" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="Q10" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="R10" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="S10" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="T10" s="7" t="s">
+      <c r="T10" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="U10" s="11" t="s">
+      <c r="U10" s="22" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="7" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B11" s="18"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="24"/>
+      <c r="H11" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="L11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="O11" s="13"/>
-      <c r="P11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="S11" s="13"/>
-      <c r="T11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="U11" s="13"/>
-    </row>
-    <row r="12" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+      <c r="L11" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11" s="24"/>
+      <c r="N11" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="O11" s="24"/>
+      <c r="P11" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="S11" s="24"/>
+      <c r="T11" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="U11" s="24"/>
+    </row>
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B12" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="P12" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="R12" s="7" t="s">
+      <c r="R12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="S12" s="8" t="s">
+      <c r="S12" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="T12" s="7" t="s">
+      <c r="T12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="U12" s="8" t="s">
+      <c r="U12" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="9" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B13" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="7" t="s">
+      <c r="H13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="22"/>
+      <c r="J13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="22"/>
+      <c r="L13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="N13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="7" t="s">
+      <c r="N13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="O13" s="22"/>
+      <c r="P13" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="R13" s="7" t="s">
+      <c r="R13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="S13" s="11" t="s">
+      <c r="S13" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="T13" s="7" t="s">
+      <c r="T13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="U13" s="11" t="s">
+      <c r="U13" s="22" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+      <c r="B14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="7" t="s">
+      <c r="C14" s="24"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="24"/>
+      <c r="H14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="24"/>
+      <c r="J14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="7" t="s">
+      <c r="K14" s="24"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="7" t="s">
+      <c r="O14" s="24"/>
+      <c r="P14" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="7" t="s">
+      <c r="Q14" s="24"/>
+      <c r="R14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="S14" s="13"/>
-      <c r="T14" s="7" t="s">
+      <c r="S14" s="24"/>
+      <c r="T14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="U14" s="13"/>
+      <c r="U14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5412,7 +5440,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="61" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/새 타령.xlsx
+++ b/sheets/민요/검수/새 타령.xlsx
@@ -4741,30 +4741,30 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="80.0" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -4788,7 +4788,7 @@
       <c r="T2" s="17"/>
       <c r="U2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>99</v>
       </c>
@@ -4850,7 +4850,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>68</v>
       </c>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>49</v>
       </c>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>49</v>
       </c>
@@ -5012,7 +5012,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>49</v>
       </c>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>49</v>
       </c>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B9" s="18"/>
       <c r="C9" s="19"/>
       <c r="D9" s="18" t="s">
@@ -5178,7 +5178,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B10" s="18"/>
       <c r="C10" s="22"/>
       <c r="D10" s="18" t="s">
@@ -5234,7 +5234,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B11" s="18"/>
       <c r="C11" s="24"/>
       <c r="D11" s="18" t="s">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B12" s="18" t="s">
         <v>77</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B13" s="20" t="s">
         <v>53</v>
       </c>
@@ -5396,7 +5396,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B14" s="18" t="s">
         <v>59</v>
       </c>
@@ -5440,7 +5440,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
